--- a/#ML_anonymized.xlsx
+++ b/#ML_anonymized.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>关注的userName</t>
+          <t>followed_userName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>粉丝的userName</t>
+          <t>follower_userName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发文量</t>
+          <t>Number of Publications</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,12 +557,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -591,12 +591,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -624,12 +624,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -656,12 +656,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -690,12 +690,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -722,12 +722,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -818,12 +818,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -852,12 +852,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -888,12 +888,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -923,12 +923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -959,12 +959,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1032,12 +1032,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1101,12 +1101,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>user_02972</t>
+          <t>user_03052</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_01118</t>
+          <t>user_01137</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1174,12 +1174,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1274,12 +1274,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1308,12 +1308,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1410,12 +1410,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1443,12 +1443,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1477,12 +1477,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1647,12 +1647,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1715,12 +1715,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1748,12 +1748,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>user_00211</t>
+          <t>user_00215</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>user_00212</t>
+          <t>user_00216</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1814,12 +1814,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1920,12 +1920,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1952,12 +1952,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1987,12 +1987,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2020,12 +2020,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2052,12 +2052,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2084,12 +2084,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>user_00069</t>
+          <t>user_00070</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>user_02203</t>
+          <t>user_02228</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2152,12 +2152,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2193,12 +2193,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2229,12 +2229,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2298,12 +2298,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2367,12 +2367,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2474,12 +2474,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2616,12 +2616,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,12 +2652,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2727,12 +2727,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,12 +2796,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,12 +2831,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>user_00962</t>
+          <t>user_00976</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>user_02477</t>
+          <t>user_02524</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2868,12 +2868,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2914,12 +2914,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2949,12 +2949,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2985,12 +2985,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3021,12 +3021,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3056,12 +3056,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3092,12 +3092,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3161,12 +3161,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3200,12 +3200,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3235,12 +3235,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3272,12 +3272,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3308,12 +3308,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3344,12 +3344,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3381,12 +3381,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3417,12 +3417,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3452,12 +3452,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3488,12 +3488,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3599,12 +3599,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>user_02071</t>
+          <t>user_02095</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>user_01246</t>
+          <t>user_01266</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3678,12 +3678,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3710,12 +3710,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3742,12 +3742,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3775,12 +3775,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3807,12 +3807,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3871,12 +3871,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3903,12 +3903,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3935,12 +3935,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3967,12 +3967,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4000,12 +4000,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4032,12 +4032,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4065,12 +4065,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4097,12 +4097,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4129,12 +4129,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,12 +4161,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4197,12 +4197,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4229,12 +4229,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4261,12 +4261,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4293,12 +4293,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4327,12 +4327,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4366,12 +4366,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4400,12 +4400,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4434,12 +4434,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4469,12 +4469,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4534,12 +4534,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4567,12 +4567,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4601,12 +4601,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4634,12 +4634,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4668,12 +4668,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4769,12 +4769,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4803,12 +4803,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4837,12 +4837,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4871,12 +4871,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4905,12 +4905,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4938,12 +4938,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5006,12 +5006,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>user_00121</t>
+          <t>user_00123</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>user_00231</t>
+          <t>user_00236</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5038,12 +5038,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5079,12 +5079,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5145,12 +5145,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5212,12 +5212,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5245,12 +5245,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5278,12 +5278,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5310,12 +5310,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5342,12 +5342,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5420,12 +5420,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5452,12 +5452,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5486,12 +5486,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5518,12 +5518,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5557,12 +5557,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5595,12 +5595,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5634,12 +5634,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5668,12 +5668,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5704,12 +5704,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5740,12 +5740,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5773,12 +5773,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5806,12 +5806,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5842,12 +5842,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5880,12 +5880,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5917,12 +5917,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5950,12 +5950,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5984,12 +5984,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6023,12 +6023,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6058,12 +6058,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6096,12 +6096,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6131,12 +6131,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6168,12 +6168,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6203,12 +6203,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6239,12 +6239,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>user_01177</t>
+          <t>user_01196</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6277,12 +6277,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6318,12 +6318,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6351,12 +6351,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6384,12 +6384,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6417,12 +6417,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6450,12 +6450,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6483,12 +6483,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6516,12 +6516,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6549,12 +6549,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6582,12 +6582,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6615,12 +6615,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6648,12 +6648,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6681,12 +6681,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6714,12 +6714,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6747,12 +6747,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6780,12 +6780,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6813,12 +6813,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6846,12 +6846,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6879,12 +6879,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6912,12 +6912,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6945,12 +6945,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>user_02215</t>
+          <t>user_02240</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>user_02216</t>
+          <t>user_02241</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6978,12 +6978,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>user_02432</t>
+          <t>user_02476</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>user_02433</t>
+          <t>user_02477</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7024,12 +7024,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7066,12 +7066,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7102,12 +7102,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7137,12 +7137,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7174,12 +7174,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7212,12 +7212,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7250,12 +7250,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7287,12 +7287,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7325,12 +7325,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7362,12 +7362,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7399,12 +7399,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7432,12 +7432,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7464,12 +7464,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7497,12 +7497,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7529,12 +7529,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7561,12 +7561,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>user_00120</t>
+          <t>user_00122</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>user_02210</t>
+          <t>user_02235</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7594,12 +7594,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>user_00915</t>
+          <t>user_00928</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>user_00916</t>
+          <t>user_00929</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7635,12 +7635,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>user_00915</t>
+          <t>user_00928</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>user_00916</t>
+          <t>user_00929</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7670,12 +7670,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>user_00915</t>
+          <t>user_00928</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>user_00916</t>
+          <t>user_00929</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7702,12 +7702,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>user_00915</t>
+          <t>user_00928</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>user_00916</t>
+          <t>user_00929</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7734,12 +7734,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>user_00915</t>
+          <t>user_00928</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>user_00916</t>
+          <t>user_00929</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7769,12 +7769,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>user_00366</t>
+          <t>user_00374</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>user_02292</t>
+          <t>user_02324</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7809,12 +7809,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7848,12 +7848,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7881,12 +7881,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7915,12 +7915,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7947,12 +7947,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7980,12 +7980,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8012,12 +8012,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8044,12 +8044,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8078,12 +8078,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8112,12 +8112,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8146,12 +8146,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8180,12 +8180,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8214,12 +8214,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8248,12 +8248,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8285,12 +8285,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8319,12 +8319,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8353,12 +8353,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8389,12 +8389,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8424,12 +8424,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8459,12 +8459,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8494,12 +8494,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8528,12 +8528,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>user_01866</t>
+          <t>user_01887</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>user_02751</t>
+          <t>user_02813</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8578,12 +8578,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8621,12 +8621,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8654,12 +8654,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8688,12 +8688,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8720,12 +8720,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8753,12 +8753,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8785,12 +8785,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8817,12 +8817,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8851,12 +8851,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8885,12 +8885,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8919,12 +8919,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8953,12 +8953,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8987,12 +8987,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9021,12 +9021,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9058,12 +9058,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9092,12 +9092,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9126,12 +9126,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9162,12 +9162,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9197,12 +9197,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9232,12 +9232,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9271,12 +9271,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9309,12 +9309,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9347,12 +9347,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9386,12 +9386,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9422,12 +9422,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9463,12 +9463,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9495,12 +9495,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9528,12 +9528,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9564,12 +9564,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9598,12 +9598,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9646,12 +9646,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,12 +9680,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9712,12 +9712,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9746,12 +9746,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9779,12 +9779,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9818,12 +9818,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9852,12 +9852,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9884,12 +9884,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9917,12 +9917,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9952,12 +9952,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>user_00126</t>
+          <t>user_00128</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>user_02213</t>
+          <t>user_02238</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9985,12 +9985,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,12 +10030,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10064,12 +10064,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10098,12 +10098,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10132,12 +10132,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10166,12 +10166,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10200,12 +10200,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10234,12 +10234,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10269,12 +10269,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10303,12 +10303,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10338,12 +10338,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10372,12 +10372,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10406,12 +10406,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10440,12 +10440,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10474,12 +10474,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10509,12 +10509,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10543,12 +10543,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10577,12 +10577,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10611,12 +10611,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10646,12 +10646,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10680,12 +10680,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>user_01709</t>
+          <t>user_01730</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>user_01710</t>
+          <t>user_01731</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10715,12 +10715,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>user_00222</t>
+          <t>user_00226</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>user_00223</t>
+          <t>user_00227</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10753,12 +10753,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10797,12 +10797,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10832,12 +10832,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10866,12 +10866,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10900,12 +10900,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10941,12 +10941,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10975,12 +10975,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11013,12 +11013,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11047,12 +11047,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11079,12 +11079,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11113,12 +11113,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11147,12 +11147,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11181,12 +11181,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11215,12 +11215,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11249,12 +11249,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11282,12 +11282,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11316,12 +11316,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11350,12 +11350,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11383,12 +11383,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11417,12 +11417,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11451,12 +11451,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>user_00554</t>
+          <t>user_00562</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>user_02665</t>
+          <t>user_02725</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11485,12 +11485,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11519,12 +11519,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -11553,12 +11553,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -11590,12 +11590,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11624,12 +11624,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -11658,12 +11658,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -11694,12 +11694,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -11730,12 +11730,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -11767,12 +11767,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -11801,12 +11801,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -11836,12 +11836,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -11870,12 +11870,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -11904,12 +11904,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -11937,12 +11937,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -11971,12 +11971,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12018,12 +12018,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12050,12 +12050,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12086,12 +12086,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12124,12 +12124,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -12158,12 +12158,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -12199,12 +12199,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -12233,12 +12233,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -12267,12 +12267,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12304,12 +12304,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -12338,12 +12338,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -12372,12 +12372,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -12408,12 +12408,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -12444,12 +12444,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -12481,12 +12481,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -12515,12 +12515,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -12550,12 +12550,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -12584,12 +12584,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -12618,12 +12618,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -12651,12 +12651,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -12685,12 +12685,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -12732,12 +12732,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -12764,12 +12764,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -12800,12 +12800,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -12838,12 +12838,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>user_01112</t>
+          <t>user_01129</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>user_01113</t>
+          <t>user_01130</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -12872,12 +12872,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -12913,12 +12913,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -12946,12 +12946,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -12979,12 +12979,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -13013,12 +13013,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -13046,12 +13046,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -13079,12 +13079,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -13112,12 +13112,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -13144,12 +13144,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -13176,12 +13176,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -13215,12 +13215,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -13254,12 +13254,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -13286,12 +13286,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13320,12 +13320,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>user_00094</t>
+          <t>user_00096</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>user_02280</t>
+          <t>user_02311</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13352,12 +13352,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13395,12 +13395,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -13427,12 +13427,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13459,12 +13459,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13492,12 +13492,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13524,12 +13524,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -13556,12 +13556,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -13588,12 +13588,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -13620,12 +13620,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -13652,12 +13652,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -13684,12 +13684,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -13717,12 +13717,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -13749,12 +13749,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -13782,12 +13782,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -13814,12 +13814,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -13846,12 +13846,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -13878,12 +13878,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -13914,12 +13914,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -13946,12 +13946,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -13978,12 +13978,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -14010,12 +14010,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>user_00877</t>
+          <t>user_00890</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>user_00878</t>
+          <t>user_00891</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -14044,12 +14044,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -14083,12 +14083,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -14116,12 +14116,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -14150,12 +14150,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -14182,12 +14182,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -14215,12 +14215,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14247,12 +14247,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -14279,12 +14279,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14313,12 +14313,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14347,12 +14347,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -14381,12 +14381,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -14415,12 +14415,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -14449,12 +14449,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14483,12 +14483,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14520,12 +14520,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14554,12 +14554,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -14588,12 +14588,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -14624,12 +14624,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -14659,12 +14659,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -14694,12 +14694,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -14729,12 +14729,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -14763,12 +14763,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -14801,12 +14801,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -14835,12 +14835,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -14867,12 +14867,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -14900,12 +14900,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -14933,12 +14933,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -14966,12 +14966,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -14999,12 +14999,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -15031,12 +15031,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -15064,12 +15064,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -15096,12 +15096,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -15128,12 +15128,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -15163,12 +15163,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -15198,12 +15198,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -15231,12 +15231,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -15264,12 +15264,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -15296,12 +15296,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -15329,12 +15329,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -15362,12 +15362,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -15394,12 +15394,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -15426,12 +15426,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>user_02836</t>
+          <t>user_02903</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>user_02673</t>
+          <t>user_02733</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -15458,12 +15458,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -15498,12 +15498,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -15530,12 +15530,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -15567,12 +15567,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -15600,12 +15600,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -15634,12 +15634,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -15668,12 +15668,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -15701,12 +15701,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -15736,12 +15736,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -15770,12 +15770,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -15803,12 +15803,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -15837,12 +15837,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -15870,12 +15870,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -15904,12 +15904,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -15938,12 +15938,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -15972,12 +15972,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -16006,12 +16006,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -16040,12 +16040,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -16075,12 +16075,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -16108,12 +16108,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -16141,12 +16141,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>user_01596</t>
+          <t>user_01617</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>user_02636</t>
+          <t>user_02693</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -16175,12 +16175,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -16214,12 +16214,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -16247,12 +16247,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -16279,12 +16279,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -16312,12 +16312,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -16345,12 +16345,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16377,12 +16377,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -16409,12 +16409,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -16441,12 +16441,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -16475,12 +16475,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -16507,12 +16507,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -16540,12 +16540,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -16572,12 +16572,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -16605,12 +16605,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -16639,12 +16639,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -16671,12 +16671,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16703,12 +16703,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -16736,12 +16736,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -16770,12 +16770,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -16802,12 +16802,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -16835,12 +16835,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -16868,12 +16868,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -16907,12 +16907,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -16940,12 +16940,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -16974,12 +16974,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -17006,12 +17006,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -17039,12 +17039,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -17071,12 +17071,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -17103,12 +17103,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -17137,12 +17137,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -17171,12 +17171,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -17205,12 +17205,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -17239,12 +17239,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -17273,12 +17273,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -17307,12 +17307,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -17344,12 +17344,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -17378,12 +17378,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -17412,12 +17412,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -17448,12 +17448,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -17483,12 +17483,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -17518,12 +17518,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -17553,12 +17553,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>user_01567</t>
+          <t>user_01588</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>user_01568</t>
+          <t>user_01589</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -17587,12 +17587,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -17626,12 +17626,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -17662,12 +17662,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -17695,12 +17695,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -17727,12 +17727,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -17760,12 +17760,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -17793,12 +17793,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -17826,12 +17826,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -17861,12 +17861,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -17894,12 +17894,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -17927,12 +17927,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -17962,12 +17962,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -17995,12 +17995,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -18028,12 +18028,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -18061,12 +18061,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -18094,12 +18094,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -18127,12 +18127,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -18159,12 +18159,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -18198,12 +18198,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -18231,12 +18231,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -18264,12 +18264,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>user_01392</t>
+          <t>user_01412</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18297,12 +18297,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18336,12 +18336,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18369,12 +18369,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -18401,12 +18401,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -18434,12 +18434,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -18467,12 +18467,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -18499,12 +18499,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -18531,12 +18531,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -18563,12 +18563,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -18597,12 +18597,12 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -18629,12 +18629,12 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -18662,12 +18662,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -18694,12 +18694,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -18727,12 +18727,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -18761,12 +18761,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -18793,12 +18793,12 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -18825,12 +18825,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -18858,12 +18858,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -18892,12 +18892,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -18924,12 +18924,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -18957,12 +18957,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>user_01804</t>
+          <t>user_01825</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>user_01805</t>
+          <t>user_01826</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -18990,12 +18990,12 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -19033,12 +19033,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -19069,12 +19069,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -19104,12 +19104,12 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -19142,12 +19142,12 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -19174,12 +19174,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -19208,12 +19208,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -19242,12 +19242,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -19277,12 +19277,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -19311,12 +19311,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -19348,12 +19348,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -19382,12 +19382,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -19418,12 +19418,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -19455,12 +19455,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -19491,12 +19491,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -19526,12 +19526,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -19561,12 +19561,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -19595,12 +19595,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -19631,12 +19631,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>user_02072</t>
+          <t>user_02096</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>user_02073</t>
+          <t>user_02097</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -19665,12 +19665,12 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -19706,12 +19706,12 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -19738,12 +19738,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -19771,12 +19771,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -19803,12 +19803,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -19835,12 +19835,12 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -19867,12 +19867,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -19900,12 +19900,12 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -19932,12 +19932,12 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -19964,12 +19964,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -19997,12 +19997,12 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -20029,12 +20029,12 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -20061,12 +20061,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -20094,12 +20094,12 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -20126,12 +20126,12 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -20158,12 +20158,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -20192,12 +20192,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -20224,12 +20224,12 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>user_00178</t>
+          <t>user_00182</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>user_00180</t>
+          <t>user_00184</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">

--- a/#ML_anonymized.xlsx
+++ b/#ML_anonymized.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13388,7 +13388,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18329,7 +18329,7 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19026,7 +19026,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
